--- a/esyluban/examples/release/DataTables/test/multi_level_title.xlsx
+++ b/esyluban/examples/release/DataTables/test/multi_level_title.xlsx
@@ -1486,21 +1486,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="L2:M2"/>
     <mergeCell ref="D2:F2"/>
-    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N3:W3"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="N2:W2"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="J3:K3"/>
     <mergeCell ref="G2:I2"/>
-    <mergeCell ref="N2:W2"/>
-    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="V4:W4"/>
     <mergeCell ref="J2:K2"/>
-    <mergeCell ref="N1:W1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="D3:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
